--- a/survey_templates/036_vehicle_interior_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/036_vehicle_interior_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_good', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'very_poor', 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_good', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'very_poor', 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'miles',_'label':_'miles'}</t>
+          <t>miles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'miles', 'label': 'miles'}</t>
+          <t>miles</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'kilometers',_'label':_'kilometers'}</t>
+          <t>kilometers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'kilometers', 'label': 'kilometers'}</t>
+          <t>kilometers</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'registered',_'label':_'registered'}</t>
+          <t>registered</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'registered', 'label': 'Registered'}</t>
+          <t>Registered</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'deregistered',_'label':_'deregistered'}</t>
+          <t>deregistered</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'deregistered', 'label': 'Deregistered'}</t>
+          <t>Deregistered</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending_registration',_'label':_'pending_registration'}</t>
+          <t>pending_registration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending_registration', 'label': 'Pending Registration'}</t>
+          <t>Pending Registration</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'pending_warranty',_'label':_'pending_warranty'}</t>
+          <t>pending_warranty</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'pending_warranty', 'label': 'Pending Warranty'}</t>
+          <t>Pending Warranty</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'standard',_'label':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'standard', 'label': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'leather',_'label':_'leather'}</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'leather', 'label': 'Leather'}</t>
+          <t>Leather</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'premium',_'label':_'premium'}</t>
+          <t>premium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'premium', 'label': 'Premium'}</t>
+          <t>Premium</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'custom',_'label':_'custom'}</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'custom', 'label': 'Custom'}</t>
+          <t>Custom</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'automatic',_'label':_'automatic'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'automatic', 'label': 'Automatic'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'manual',_'label':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'manual', 'label': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'semi-automatic',_'label':_'semi-automatic'}</t>
+          <t>semi-automatic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'semi-automatic', 'label': 'Semi-Automatic'}</t>
+          <t>Semi-Automatic</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'gasoline',_'label':_'gasoline'}</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'gasoline', 'label': 'Gasoline'}</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'diesel',_'label':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'diesel', 'label': 'Diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'electric',_'label':_'electric'}</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'electric', 'label': 'Electric'}</t>
+          <t>Electric</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'front_wheel_drive',_'label':_'front_wheel_drive'}</t>
+          <t>front_wheel_drive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'front_wheel_drive', 'label': 'Front Wheel Drive'}</t>
+          <t>Front Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'rear_wheel_drive',_'label':_'rear_wheel_drive'}</t>
+          <t>rear_wheel_drive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'rear_wheel_drive', 'label': 'Rear Wheel Drive'}</t>
+          <t>Rear Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'all_wheel_drive',_'label':_'all_wheel_drive'}</t>
+          <t>all_wheel_drive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'all_wheel_drive', 'label': 'All Wheel Drive'}</t>
+          <t>All Wheel Drive</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cloth',_'label':_'cloth'}</t>
+          <t>cloth</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'cloth', 'label': 'Cloth'}</t>
+          <t>Cloth</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'leather',_'label':_'leather'}</t>
+          <t>leather</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'leather', 'label': 'Leather'}</t>
+          <t>Leather</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'vinyl',_'label':_'vinyl'}</t>
+          <t>vinyl</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'vinyl', 'label': 'Vinyl'}</t>
+          <t>Vinyl</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dual',_'label':_'dual'}</t>
+          <t>dual</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'dual', 'label': 'Dual'}</t>
+          <t>Dual</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'single',_'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'single', 'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'none',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'none', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'front',_'label':_'front'}</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'front', 'label': 'Front'}</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'rear',_'label':_'rear'}</t>
+          <t>rear</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'rear', 'label': 'Rear'}</t>
+          <t>Rear</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_poor',_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'very_poor', 'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
